--- a/famille/data/data_general.xlsx
+++ b/famille/data/data_general.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Mes Sites\babouch\famille\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABD8B8C0-F016-4A24-A88C-9A4F3BCBB5BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{34E9302E-0A40-42BE-8FEC-D7DCBB15DB2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{2ED77E2F-0DF7-480A-8A8F-EEC0E1A3C4F7}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{2ED77E2F-0DF7-480A-8A8F-EEC0E1A3C4F7}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="790" uniqueCount="255">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="906" uniqueCount="278">
   <si>
     <t>Génération</t>
   </si>
@@ -804,6 +804,75 @@
   </si>
   <si>
     <t>Odile</t>
+  </si>
+  <si>
+    <t>J-Baptiste</t>
+  </si>
+  <si>
+    <t>Charpentier</t>
+  </si>
+  <si>
+    <t>JEANNET</t>
+  </si>
+  <si>
+    <t>Monique</t>
+  </si>
+  <si>
+    <t>Marinier</t>
+  </si>
+  <si>
+    <t>Fayence</t>
+  </si>
+  <si>
+    <t>BERLU</t>
+  </si>
+  <si>
+    <t>Tailleur d'habits</t>
+  </si>
+  <si>
+    <t>TEMPIER</t>
+  </si>
+  <si>
+    <t>Genviève</t>
+  </si>
+  <si>
+    <t>MICHEL</t>
+  </si>
+  <si>
+    <t>Aix-en-Provence</t>
+  </si>
+  <si>
+    <t>Pignans (83)</t>
+  </si>
+  <si>
+    <t>RIMBAUD</t>
+  </si>
+  <si>
+    <t>Cannonier</t>
+  </si>
+  <si>
+    <t>Bras (83)</t>
+  </si>
+  <si>
+    <t>Journalier à l'arsenal</t>
+  </si>
+  <si>
+    <t>Anne Rose</t>
+  </si>
+  <si>
+    <t>COCHET</t>
+  </si>
+  <si>
+    <t>Pélagie</t>
+  </si>
+  <si>
+    <t>GODIVIER</t>
+  </si>
+  <si>
+    <t>Bazouges (53)</t>
+  </si>
+  <si>
+    <t>Ménil (53)</t>
   </si>
 </sst>
 </file>
@@ -1186,7 +1255,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77AA109F-713A-466A-B871-A566CBDE270F}">
-  <dimension ref="A1:M169"/>
+  <dimension ref="A1:M244"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="4" width="16" customWidth="1"/>
@@ -5418,18 +5487,50 @@
         <v>42</v>
       </c>
     </row>
+    <row r="117" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A117">
+        <v>8</v>
+      </c>
+      <c r="B117">
+        <v>128</v>
+      </c>
+      <c r="C117" t="s">
+        <v>87</v>
+      </c>
+      <c r="D117" t="s">
+        <v>22</v>
+      </c>
+      <c r="E117" t="s">
+        <v>147</v>
+      </c>
+      <c r="F117" t="s">
+        <v>147</v>
+      </c>
+      <c r="G117" t="s">
+        <v>147</v>
+      </c>
+      <c r="H117" t="s">
+        <v>147</v>
+      </c>
+      <c r="J117" t="s">
+        <v>147</v>
+      </c>
+      <c r="K117" t="s">
+        <v>147</v>
+      </c>
+    </row>
     <row r="118" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A118">
         <v>8</v>
       </c>
       <c r="B118">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C118" t="s">
-        <v>87</v>
+        <v>147</v>
       </c>
       <c r="D118" t="s">
-        <v>22</v>
+        <v>147</v>
       </c>
       <c r="E118" t="s">
         <v>147</v>
@@ -5451,22 +5552,49 @@
       </c>
     </row>
     <row r="119" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A119">
+        <v>8</v>
+      </c>
       <c r="B119">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C119" t="s">
-        <v>147</v>
+        <v>148</v>
+      </c>
+      <c r="D119" t="s">
+        <v>242</v>
+      </c>
+      <c r="E119" t="s">
+        <v>147</v>
+      </c>
+      <c r="F119" t="s">
+        <v>147</v>
+      </c>
+      <c r="G119">
+        <v>1698</v>
+      </c>
+      <c r="H119" t="s">
+        <v>31</v>
+      </c>
+      <c r="J119">
+        <v>1750</v>
+      </c>
+      <c r="K119" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="120" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A120">
+        <v>8</v>
+      </c>
       <c r="B120">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C120" t="s">
-        <v>148</v>
+        <v>243</v>
       </c>
       <c r="D120" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="E120" t="s">
         <v>147</v>
@@ -5480,54 +5608,60 @@
       <c r="H120" t="s">
         <v>31</v>
       </c>
-      <c r="J120">
-        <v>1750</v>
+      <c r="J120" t="s">
+        <v>147</v>
       </c>
       <c r="K120" t="s">
-        <v>31</v>
+        <v>147</v>
       </c>
     </row>
     <row r="121" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A121">
+        <v>8</v>
+      </c>
       <c r="B121">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C121" t="s">
-        <v>243</v>
+        <v>89</v>
       </c>
       <c r="D121" t="s">
-        <v>244</v>
-      </c>
-      <c r="E121" t="s">
-        <v>147</v>
+        <v>245</v>
+      </c>
+      <c r="E121">
+        <v>1677</v>
       </c>
       <c r="F121" t="s">
-        <v>147</v>
+        <v>95</v>
       </c>
       <c r="G121">
-        <v>1698</v>
+        <v>1703</v>
       </c>
       <c r="H121" t="s">
-        <v>31</v>
-      </c>
-      <c r="J121" t="s">
-        <v>147</v>
+        <v>95</v>
+      </c>
+      <c r="J121">
+        <v>1733</v>
       </c>
       <c r="K121" t="s">
-        <v>147</v>
+        <v>95</v>
       </c>
     </row>
     <row r="122" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A122">
+        <v>8</v>
+      </c>
       <c r="B122">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C122" t="s">
-        <v>89</v>
+        <v>246</v>
       </c>
       <c r="D122" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="E122">
-        <v>1677</v>
+        <v>1683</v>
       </c>
       <c r="F122" t="s">
         <v>95</v>
@@ -5539,56 +5673,62 @@
         <v>95</v>
       </c>
       <c r="J122">
-        <v>1733</v>
+        <v>1744</v>
       </c>
       <c r="K122" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="123" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A123">
+        <v>8</v>
+      </c>
       <c r="B123">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C123" t="s">
-        <v>246</v>
+        <v>154</v>
       </c>
       <c r="D123" t="s">
-        <v>247</v>
+        <v>200</v>
       </c>
       <c r="E123">
-        <v>1683</v>
+        <v>1681</v>
       </c>
       <c r="F123" t="s">
-        <v>95</v>
+        <v>31</v>
       </c>
       <c r="G123">
-        <v>1703</v>
+        <v>1705</v>
       </c>
       <c r="H123" t="s">
-        <v>95</v>
+        <v>31</v>
       </c>
       <c r="J123">
-        <v>1744</v>
+        <v>1720</v>
       </c>
       <c r="K123" t="s">
-        <v>95</v>
+        <v>31</v>
       </c>
     </row>
     <row r="124" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A124">
+        <v>8</v>
+      </c>
       <c r="B124">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C124" t="s">
-        <v>154</v>
+        <v>248</v>
       </c>
       <c r="D124" t="s">
-        <v>200</v>
-      </c>
-      <c r="E124">
-        <v>1681</v>
+        <v>249</v>
+      </c>
+      <c r="E124" t="s">
+        <v>147</v>
       </c>
       <c r="F124" t="s">
-        <v>31</v>
+        <v>147</v>
       </c>
       <c r="G124">
         <v>1705</v>
@@ -5597,76 +5737,106 @@
         <v>31</v>
       </c>
       <c r="J124">
-        <v>1720</v>
+        <v>1753</v>
       </c>
       <c r="K124" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="125" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A125">
+        <v>8</v>
+      </c>
       <c r="B125">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C125" t="s">
-        <v>248</v>
-      </c>
-      <c r="D125" t="s">
-        <v>249</v>
-      </c>
-      <c r="E125" t="s">
-        <v>147</v>
-      </c>
-      <c r="F125" t="s">
-        <v>147</v>
-      </c>
-      <c r="G125">
-        <v>1705</v>
-      </c>
-      <c r="H125" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="126" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A126">
+        <v>8</v>
+      </c>
+      <c r="B126">
+        <v>137</v>
+      </c>
+      <c r="C126" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="127" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A127">
+        <v>8</v>
+      </c>
+      <c r="B127">
+        <v>138</v>
+      </c>
+      <c r="C127" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="128" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A128">
+        <v>8</v>
+      </c>
+      <c r="B128">
+        <v>139</v>
+      </c>
+      <c r="C128" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="129" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A129">
+        <v>8</v>
+      </c>
+      <c r="B129">
+        <v>140</v>
+      </c>
+      <c r="C129" t="s">
+        <v>93</v>
+      </c>
+      <c r="D129" t="s">
+        <v>157</v>
+      </c>
+      <c r="E129">
+        <v>1685</v>
+      </c>
+      <c r="F129" t="s">
         <v>31</v>
       </c>
-      <c r="J125">
-        <v>1753</v>
-      </c>
-      <c r="K125" t="s">
+      <c r="G129">
+        <v>1712</v>
+      </c>
+      <c r="H129" t="s">
+        <v>251</v>
+      </c>
+      <c r="J129">
+        <v>1721</v>
+      </c>
+      <c r="K129" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="126" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="B126">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="127" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="B127">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="128" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="B128">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="129" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B129">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="130" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A130">
+        <v>8</v>
+      </c>
       <c r="B130">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C130" t="s">
-        <v>93</v>
+        <v>250</v>
       </c>
       <c r="D130" t="s">
-        <v>157</v>
-      </c>
-      <c r="E130">
-        <v>1685</v>
+        <v>149</v>
+      </c>
+      <c r="E130" t="s">
+        <v>147</v>
       </c>
       <c r="F130" t="s">
-        <v>31</v>
+        <v>147</v>
       </c>
       <c r="G130">
         <v>1712</v>
@@ -5675,53 +5845,59 @@
         <v>251</v>
       </c>
       <c r="J130">
-        <v>1721</v>
+        <v>1733</v>
       </c>
       <c r="K130" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="131" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A131">
+        <v>8</v>
+      </c>
       <c r="B131">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C131" t="s">
-        <v>250</v>
+        <v>158</v>
       </c>
       <c r="D131" t="s">
-        <v>149</v>
-      </c>
-      <c r="E131" t="s">
-        <v>147</v>
+        <v>252</v>
       </c>
       <c r="F131" t="s">
-        <v>147</v>
+        <v>95</v>
       </c>
       <c r="G131">
-        <v>1712</v>
+        <v>1708</v>
       </c>
       <c r="H131" t="s">
-        <v>251</v>
+        <v>95</v>
       </c>
       <c r="J131">
-        <v>1733</v>
+        <v>1761</v>
       </c>
       <c r="K131" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="132" spans="2:11" x14ac:dyDescent="0.25">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="132" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A132">
+        <v>8</v>
+      </c>
       <c r="B132">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C132" t="s">
-        <v>158</v>
+        <v>253</v>
       </c>
       <c r="D132" t="s">
-        <v>252</v>
+        <v>254</v>
+      </c>
+      <c r="E132" t="s">
+        <v>147</v>
       </c>
       <c r="F132" t="s">
-        <v>95</v>
+        <v>147</v>
       </c>
       <c r="G132">
         <v>1708</v>
@@ -5730,21 +5906,24 @@
         <v>95</v>
       </c>
       <c r="J132">
-        <v>1761</v>
+        <v>1733</v>
       </c>
       <c r="K132" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="133" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A133">
+        <v>8</v>
+      </c>
       <c r="B133">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C133" t="s">
-        <v>253</v>
+        <v>33</v>
       </c>
       <c r="D133" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E133" t="s">
         <v>147</v>
@@ -5753,26 +5932,589 @@
         <v>147</v>
       </c>
       <c r="G133">
-        <v>1708</v>
+        <v>1736</v>
       </c>
       <c r="H133" t="s">
-        <v>95</v>
-      </c>
-      <c r="J133">
-        <v>1733</v>
+        <v>12</v>
+      </c>
+      <c r="I133" t="s">
+        <v>256</v>
+      </c>
+      <c r="J133" t="s">
+        <v>147</v>
       </c>
       <c r="K133" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="134" spans="2:11" x14ac:dyDescent="0.25">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="134" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A134">
+        <v>8</v>
+      </c>
       <c r="B134">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="135" spans="2:11" x14ac:dyDescent="0.25">
+        <v>145</v>
+      </c>
+      <c r="C134" t="s">
+        <v>257</v>
+      </c>
+      <c r="D134" t="s">
+        <v>258</v>
+      </c>
+      <c r="E134">
+        <v>1709</v>
+      </c>
+      <c r="F134" t="s">
+        <v>12</v>
+      </c>
+      <c r="G134">
+        <v>1736</v>
+      </c>
+      <c r="H134" t="s">
+        <v>12</v>
+      </c>
+      <c r="J134">
+        <v>1774</v>
+      </c>
+      <c r="K134" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="135" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A135">
+        <v>8</v>
+      </c>
       <c r="B135">
-        <v>145</v>
+        <v>146</v>
+      </c>
+      <c r="C135" t="s">
+        <v>160</v>
+      </c>
+      <c r="D135" t="s">
+        <v>101</v>
+      </c>
+      <c r="E135" t="s">
+        <v>147</v>
+      </c>
+      <c r="F135" t="s">
+        <v>147</v>
+      </c>
+      <c r="G135">
+        <v>1726</v>
+      </c>
+      <c r="H135" t="s">
+        <v>12</v>
+      </c>
+      <c r="I135" t="s">
+        <v>259</v>
+      </c>
+      <c r="J135">
+        <v>1780</v>
+      </c>
+      <c r="K135" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="136" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A136">
+        <v>8</v>
+      </c>
+      <c r="B136">
+        <v>147</v>
+      </c>
+      <c r="C136" t="s">
+        <v>47</v>
+      </c>
+      <c r="D136" t="s">
+        <v>117</v>
+      </c>
+      <c r="E136" t="s">
+        <v>147</v>
+      </c>
+      <c r="F136" t="s">
+        <v>260</v>
+      </c>
+      <c r="G136">
+        <v>1726</v>
+      </c>
+      <c r="H136" t="s">
+        <v>12</v>
+      </c>
+      <c r="J136">
+        <v>1782</v>
+      </c>
+      <c r="K136" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="137" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A137">
+        <v>8</v>
+      </c>
+      <c r="B137">
+        <v>148</v>
+      </c>
+      <c r="C137" t="s">
+        <v>98</v>
+      </c>
+      <c r="D137" t="s">
+        <v>114</v>
+      </c>
+      <c r="E137" t="s">
+        <v>147</v>
+      </c>
+      <c r="J137" t="s">
+        <v>147</v>
+      </c>
+      <c r="K137" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="138" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A138">
+        <v>8</v>
+      </c>
+      <c r="B138">
+        <v>149</v>
+      </c>
+      <c r="C138" t="s">
+        <v>263</v>
+      </c>
+      <c r="D138" t="s">
+        <v>264</v>
+      </c>
+      <c r="E138" t="s">
+        <v>147</v>
+      </c>
+      <c r="J138" t="s">
+        <v>147</v>
+      </c>
+      <c r="K138" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="139" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A139">
+        <v>8</v>
+      </c>
+      <c r="B139">
+        <v>150</v>
+      </c>
+      <c r="C139" t="s">
+        <v>163</v>
+      </c>
+      <c r="D139" t="s">
+        <v>101</v>
+      </c>
+      <c r="E139" t="s">
+        <v>147</v>
+      </c>
+      <c r="F139" t="s">
+        <v>147</v>
+      </c>
+      <c r="G139">
+        <v>1734</v>
+      </c>
+      <c r="H139" t="s">
+        <v>266</v>
+      </c>
+      <c r="J139" t="s">
+        <v>147</v>
+      </c>
+      <c r="K139" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="140" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A140">
+        <v>8</v>
+      </c>
+      <c r="B140">
+        <v>151</v>
+      </c>
+      <c r="C140" t="s">
+        <v>265</v>
+      </c>
+      <c r="D140" t="s">
+        <v>21</v>
+      </c>
+      <c r="E140" t="s">
+        <v>147</v>
+      </c>
+      <c r="F140" t="s">
+        <v>147</v>
+      </c>
+      <c r="G140">
+        <v>1734</v>
+      </c>
+      <c r="H140" t="s">
+        <v>266</v>
+      </c>
+      <c r="J140" t="s">
+        <v>147</v>
+      </c>
+      <c r="K140" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="141" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A141">
+        <v>8</v>
+      </c>
+      <c r="B141">
+        <v>152</v>
+      </c>
+      <c r="C141" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="142" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A142">
+        <v>8</v>
+      </c>
+      <c r="B142">
+        <v>153</v>
+      </c>
+      <c r="C142" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="143" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A143">
+        <v>8</v>
+      </c>
+      <c r="B143">
+        <v>154</v>
+      </c>
+      <c r="C143" t="s">
+        <v>166</v>
+      </c>
+      <c r="D143" t="s">
+        <v>153</v>
+      </c>
+      <c r="I143" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="144" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A144">
+        <v>8</v>
+      </c>
+      <c r="B144">
+        <v>155</v>
+      </c>
+      <c r="C144" t="s">
+        <v>261</v>
+      </c>
+      <c r="D144" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="145" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A145">
+        <v>8</v>
+      </c>
+      <c r="B145">
+        <v>156</v>
+      </c>
+      <c r="C145" t="s">
+        <v>103</v>
+      </c>
+      <c r="D145" t="s">
+        <v>114</v>
+      </c>
+      <c r="E145">
+        <v>1718</v>
+      </c>
+      <c r="F145" t="s">
+        <v>267</v>
+      </c>
+      <c r="G145">
+        <v>1739</v>
+      </c>
+      <c r="H145" t="s">
+        <v>12</v>
+      </c>
+      <c r="I145" t="s">
+        <v>269</v>
+      </c>
+      <c r="J145" t="s">
+        <v>147</v>
+      </c>
+      <c r="K145" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="146" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A146">
+        <v>8</v>
+      </c>
+      <c r="B146">
+        <v>157</v>
+      </c>
+      <c r="C146" t="s">
+        <v>268</v>
+      </c>
+      <c r="D146" t="s">
+        <v>21</v>
+      </c>
+      <c r="E146" t="s">
+        <v>147</v>
+      </c>
+      <c r="F146" t="s">
+        <v>270</v>
+      </c>
+      <c r="G146">
+        <v>1739</v>
+      </c>
+      <c r="H146" t="s">
+        <v>12</v>
+      </c>
+      <c r="J146">
+        <v>1783</v>
+      </c>
+      <c r="K146" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="147" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A147">
+        <v>8</v>
+      </c>
+      <c r="B147">
+        <v>158</v>
+      </c>
+      <c r="C147" t="s">
+        <v>169</v>
+      </c>
+      <c r="D147" t="s">
+        <v>114</v>
+      </c>
+      <c r="E147">
+        <v>1721</v>
+      </c>
+      <c r="F147" t="s">
+        <v>267</v>
+      </c>
+      <c r="G147">
+        <v>1744</v>
+      </c>
+      <c r="H147" t="s">
+        <v>12</v>
+      </c>
+      <c r="I147" t="s">
+        <v>271</v>
+      </c>
+      <c r="J147">
+        <v>1785</v>
+      </c>
+      <c r="K147" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="148" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A148">
+        <v>8</v>
+      </c>
+      <c r="B148">
+        <v>159</v>
+      </c>
+      <c r="C148" t="s">
+        <v>216</v>
+      </c>
+      <c r="D148" t="s">
+        <v>272</v>
+      </c>
+      <c r="E148" t="s">
+        <v>147</v>
+      </c>
+      <c r="F148" t="s">
+        <v>12</v>
+      </c>
+      <c r="G148">
+        <v>1744</v>
+      </c>
+      <c r="H148" t="s">
+        <v>12</v>
+      </c>
+      <c r="J148">
+        <v>1803</v>
+      </c>
+      <c r="K148" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="149" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A149">
+        <v>8</v>
+      </c>
+      <c r="B149">
+        <v>160</v>
+      </c>
+      <c r="C149" t="s">
+        <v>28</v>
+      </c>
+      <c r="D149" t="s">
+        <v>82</v>
+      </c>
+      <c r="E149">
+        <v>1709</v>
+      </c>
+      <c r="F149" t="s">
+        <v>107</v>
+      </c>
+      <c r="G149">
+        <v>1732</v>
+      </c>
+      <c r="H149" t="s">
+        <v>107</v>
+      </c>
+      <c r="J149">
+        <v>1789</v>
+      </c>
+      <c r="K149" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="150" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A150">
+        <v>8</v>
+      </c>
+      <c r="B150">
+        <v>161</v>
+      </c>
+      <c r="C150" t="s">
+        <v>273</v>
+      </c>
+      <c r="D150" t="s">
+        <v>274</v>
+      </c>
+      <c r="E150">
+        <v>1707</v>
+      </c>
+      <c r="F150" t="s">
+        <v>107</v>
+      </c>
+      <c r="G150">
+        <v>1732</v>
+      </c>
+      <c r="H150" t="s">
+        <v>107</v>
+      </c>
+      <c r="J150">
+        <v>1792</v>
+      </c>
+      <c r="K150" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="151" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A151">
+        <v>8</v>
+      </c>
+      <c r="B151">
+        <v>162</v>
+      </c>
+      <c r="C151" t="s">
+        <v>28</v>
+      </c>
+      <c r="D151" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="152" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A152">
+        <v>8</v>
+      </c>
+      <c r="B152">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="153" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A153">
+        <v>8</v>
+      </c>
+      <c r="B153">
+        <v>164</v>
+      </c>
+      <c r="C153" t="s">
+        <v>109</v>
+      </c>
+      <c r="D153" t="s">
+        <v>141</v>
+      </c>
+      <c r="E153">
+        <v>1699</v>
+      </c>
+      <c r="F153" t="s">
+        <v>276</v>
+      </c>
+      <c r="G153">
+        <v>1725</v>
+      </c>
+      <c r="H153" t="s">
+        <v>277</v>
+      </c>
+      <c r="J153">
+        <v>1778</v>
+      </c>
+      <c r="K153" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="154" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A154">
+        <v>8</v>
+      </c>
+      <c r="B154">
+        <v>165</v>
+      </c>
+      <c r="C154" t="s">
+        <v>275</v>
+      </c>
+      <c r="D154" t="s">
+        <v>94</v>
+      </c>
+      <c r="E154">
+        <v>1702</v>
+      </c>
+      <c r="F154" t="s">
+        <v>277</v>
+      </c>
+      <c r="G154">
+        <v>1725</v>
+      </c>
+      <c r="H154" t="s">
+        <v>277</v>
+      </c>
+      <c r="J154" t="s">
+        <v>147</v>
+      </c>
+      <c r="K154" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="155" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A155">
+        <v>8</v>
+      </c>
+      <c r="B155">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="156" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A156">
+        <v>8</v>
+      </c>
+      <c r="B156">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="157" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A157">
+        <v>8</v>
+      </c>
+      <c r="B157">
+        <v>168</v>
       </c>
     </row>
     <row r="158" spans="1:11" x14ac:dyDescent="0.25">
@@ -5780,253 +6522,886 @@
         <v>8</v>
       </c>
       <c r="B158">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="159" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A159">
+        <v>8</v>
+      </c>
+      <c r="B159">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="160" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A160">
+        <v>8</v>
+      </c>
+      <c r="B160">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="161" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A161">
+        <v>8</v>
+      </c>
+      <c r="B161">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="162" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A162">
+        <v>8</v>
+      </c>
+      <c r="B162">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="163" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A163">
+        <v>8</v>
+      </c>
+      <c r="B163">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="164" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A164">
+        <v>8</v>
+      </c>
+      <c r="B164">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="165" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A165">
+        <v>8</v>
+      </c>
+      <c r="B165">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="166" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A166">
+        <v>8</v>
+      </c>
+      <c r="B166">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="167" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A167">
+        <v>8</v>
+      </c>
+      <c r="B167">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="168" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A168">
+        <v>8</v>
+      </c>
+      <c r="B168">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="169" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A169">
+        <v>8</v>
+      </c>
+      <c r="B169">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="170" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A170">
+        <v>8</v>
+      </c>
+      <c r="B170">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="171" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A171">
+        <v>8</v>
+      </c>
+      <c r="B171">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="172" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A172">
+        <v>8</v>
+      </c>
+      <c r="B172">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="173" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A173">
+        <v>8</v>
+      </c>
+      <c r="B173">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="174" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A174">
+        <v>8</v>
+      </c>
+      <c r="B174">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="175" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A175">
+        <v>8</v>
+      </c>
+      <c r="B175">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="176" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A176">
+        <v>8</v>
+      </c>
+      <c r="B176">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="177" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A177">
+        <v>8</v>
+      </c>
+      <c r="B177">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="178" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A178">
+        <v>8</v>
+      </c>
+      <c r="B178">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="179" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A179">
+        <v>8</v>
+      </c>
+      <c r="B179">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="180" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A180">
+        <v>8</v>
+      </c>
+      <c r="B180">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="181" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A181">
+        <v>8</v>
+      </c>
+      <c r="B181">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="182" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A182">
+        <v>8</v>
+      </c>
+      <c r="B182">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="183" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A183">
+        <v>8</v>
+      </c>
+      <c r="B183">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="184" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A184">
+        <v>8</v>
+      </c>
+      <c r="B184">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="185" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A185">
+        <v>8</v>
+      </c>
+      <c r="B185">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="186" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A186">
+        <v>8</v>
+      </c>
+      <c r="B186">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="187" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A187">
+        <v>8</v>
+      </c>
+      <c r="B187">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="188" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A188">
+        <v>8</v>
+      </c>
+      <c r="B188">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="189" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A189">
+        <v>8</v>
+      </c>
+      <c r="B189">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="190" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A190">
+        <v>8</v>
+      </c>
+      <c r="B190">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="191" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A191">
+        <v>8</v>
+      </c>
+      <c r="B191">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="192" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A192">
+        <v>8</v>
+      </c>
+      <c r="B192">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="193" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A193">
+        <v>8</v>
+      </c>
+      <c r="B193">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="194" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A194">
+        <v>8</v>
+      </c>
+      <c r="B194">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="195" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A195">
+        <v>8</v>
+      </c>
+      <c r="B195">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="196" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A196">
+        <v>8</v>
+      </c>
+      <c r="B196">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="197" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A197">
+        <v>8</v>
+      </c>
+      <c r="B197">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="198" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A198">
+        <v>8</v>
+      </c>
+      <c r="B198">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="199" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A199">
+        <v>8</v>
+      </c>
+      <c r="B199">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="200" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A200">
+        <v>8</v>
+      </c>
+      <c r="B200">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="201" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A201">
+        <v>8</v>
+      </c>
+      <c r="B201">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="202" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A202">
+        <v>8</v>
+      </c>
+      <c r="B202">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="203" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A203">
+        <v>8</v>
+      </c>
+      <c r="B203">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="204" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A204">
+        <v>8</v>
+      </c>
+      <c r="B204">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="205" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A205">
+        <v>8</v>
+      </c>
+      <c r="B205">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="206" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A206">
+        <v>8</v>
+      </c>
+      <c r="B206">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="207" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A207">
+        <v>8</v>
+      </c>
+      <c r="B207">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="208" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A208">
+        <v>8</v>
+      </c>
+      <c r="B208">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="209" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A209">
+        <v>8</v>
+      </c>
+      <c r="B209">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="210" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A210">
+        <v>8</v>
+      </c>
+      <c r="B210">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="211" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A211">
+        <v>8</v>
+      </c>
+      <c r="B211">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="212" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A212">
+        <v>8</v>
+      </c>
+      <c r="B212">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="213" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A213">
+        <v>8</v>
+      </c>
+      <c r="B213">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="214" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A214">
+        <v>8</v>
+      </c>
+      <c r="B214">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="215" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A215">
+        <v>8</v>
+      </c>
+      <c r="B215">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="216" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A216">
+        <v>8</v>
+      </c>
+      <c r="B216">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="217" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A217">
+        <v>8</v>
+      </c>
+      <c r="B217">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="218" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A218">
+        <v>8</v>
+      </c>
+      <c r="B218">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="219" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A219">
+        <v>8</v>
+      </c>
+      <c r="B219">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="220" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A220">
+        <v>8</v>
+      </c>
+      <c r="B220">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="221" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A221">
+        <v>8</v>
+      </c>
+      <c r="B221">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="222" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A222">
+        <v>8</v>
+      </c>
+      <c r="B222">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="223" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A223">
+        <v>8</v>
+      </c>
+      <c r="B223">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="224" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A224">
+        <v>8</v>
+      </c>
+      <c r="B224">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="225" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A225">
+        <v>8</v>
+      </c>
+      <c r="B225">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="226" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A226">
+        <v>8</v>
+      </c>
+      <c r="B226">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="227" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A227">
+        <v>8</v>
+      </c>
+      <c r="B227">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="228" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A228">
+        <v>8</v>
+      </c>
+      <c r="B228">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="229" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A229">
+        <v>8</v>
+      </c>
+      <c r="B229">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="230" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A230">
+        <v>8</v>
+      </c>
+      <c r="B230">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="231" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A231">
+        <v>8</v>
+      </c>
+      <c r="B231">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="232" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A232">
+        <v>8</v>
+      </c>
+      <c r="B232">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="233" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A233">
+        <v>8</v>
+      </c>
+      <c r="B233">
         <v>244</v>
       </c>
-      <c r="C158" t="s">
+      <c r="C233" t="s">
         <v>143</v>
       </c>
-      <c r="D158" t="s">
+      <c r="D233" t="s">
         <v>228</v>
       </c>
-      <c r="E158">
+      <c r="E233">
         <v>1707</v>
       </c>
-      <c r="F158" t="s">
+      <c r="F233" t="s">
         <v>233</v>
       </c>
-      <c r="G158">
+      <c r="G233">
         <v>1735</v>
       </c>
-      <c r="H158" t="s">
+      <c r="H233" t="s">
         <v>236</v>
       </c>
-      <c r="J158" t="s">
-        <v>147</v>
-      </c>
-      <c r="K158" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="159" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B159">
+      <c r="J233" t="s">
+        <v>147</v>
+      </c>
+      <c r="K233" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="234" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A234">
+        <v>8</v>
+      </c>
+      <c r="B234">
         <v>245</v>
       </c>
-      <c r="C159" t="s">
+      <c r="C234" t="s">
         <v>234</v>
       </c>
-      <c r="D159" t="s">
+      <c r="D234" t="s">
         <v>21</v>
       </c>
-      <c r="E159" t="s">
+      <c r="E234" t="s">
         <v>235</v>
       </c>
-      <c r="F159" t="s">
+      <c r="F234" t="s">
         <v>236</v>
       </c>
-      <c r="G159">
+      <c r="G234">
         <v>1735</v>
       </c>
-      <c r="H159" t="s">
+      <c r="H234" t="s">
         <v>236</v>
       </c>
-      <c r="J159" t="s">
-        <v>147</v>
-      </c>
-      <c r="K159" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="160" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B160">
+      <c r="J234" t="s">
+        <v>147</v>
+      </c>
+      <c r="K234" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="235" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A235">
+        <v>8</v>
+      </c>
+      <c r="B235">
         <v>246</v>
       </c>
-      <c r="C160" t="s">
+      <c r="C235" t="s">
         <v>224</v>
       </c>
-      <c r="D160" t="s">
+      <c r="D235" t="s">
         <v>237</v>
       </c>
-      <c r="E160" t="s">
-        <v>147</v>
-      </c>
-      <c r="F160" t="s">
-        <v>147</v>
-      </c>
-      <c r="G160">
+      <c r="E235" t="s">
+        <v>147</v>
+      </c>
+      <c r="F235" t="s">
+        <v>147</v>
+      </c>
+      <c r="G235">
         <v>1735</v>
       </c>
-      <c r="H160" t="s">
+      <c r="H235" t="s">
         <v>236</v>
       </c>
-      <c r="J160" t="s">
-        <v>147</v>
-      </c>
-      <c r="K160" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="161" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B161">
+      <c r="J235" t="s">
+        <v>147</v>
+      </c>
+      <c r="K235" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="236" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A236">
+        <v>8</v>
+      </c>
+      <c r="B236">
         <v>247</v>
       </c>
-      <c r="C161" t="s">
+      <c r="C236" t="s">
         <v>238</v>
       </c>
-      <c r="D161" t="s">
+      <c r="D236" t="s">
         <v>25</v>
       </c>
-      <c r="E161" t="s">
-        <v>147</v>
-      </c>
-      <c r="F161" t="s">
-        <v>147</v>
-      </c>
-      <c r="G161">
+      <c r="E236" t="s">
+        <v>147</v>
+      </c>
+      <c r="F236" t="s">
+        <v>147</v>
+      </c>
+      <c r="G236">
         <v>1735</v>
       </c>
-      <c r="H161" t="s">
+      <c r="H236" t="s">
         <v>236</v>
       </c>
-      <c r="J161" t="s">
-        <v>147</v>
-      </c>
-      <c r="K161" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="162" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B162">
+      <c r="J236" t="s">
+        <v>147</v>
+      </c>
+      <c r="K236" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="237" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A237">
+        <v>8</v>
+      </c>
+      <c r="B237">
         <v>248</v>
       </c>
     </row>
-    <row r="163" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B163">
+    <row r="238" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A238">
+        <v>8</v>
+      </c>
+      <c r="B238">
         <v>249</v>
       </c>
     </row>
-    <row r="164" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B164">
+    <row r="239" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A239">
+        <v>8</v>
+      </c>
+      <c r="B239">
         <v>250</v>
       </c>
     </row>
-    <row r="165" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B165">
+    <row r="240" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A240">
+        <v>8</v>
+      </c>
+      <c r="B240">
         <v>251</v>
       </c>
     </row>
-    <row r="166" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B166">
+    <row r="241" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A241">
+        <v>8</v>
+      </c>
+      <c r="B241">
         <v>252</v>
       </c>
-      <c r="C166" t="s">
+      <c r="C241" t="s">
         <v>151</v>
       </c>
-      <c r="D166" t="s">
+      <c r="D241" t="s">
         <v>152</v>
       </c>
-      <c r="E166" t="s">
-        <v>147</v>
-      </c>
-      <c r="F166" t="s">
+      <c r="E241" t="s">
+        <v>147</v>
+      </c>
+      <c r="F241" t="s">
         <v>240</v>
       </c>
-      <c r="G166">
+      <c r="G241">
         <v>1770</v>
       </c>
-      <c r="H166" t="s">
+      <c r="H241" t="s">
         <v>232</v>
       </c>
-      <c r="J166" t="s">
-        <v>147</v>
-      </c>
-      <c r="K166" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="167" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B167">
+      <c r="J241" t="s">
+        <v>147</v>
+      </c>
+      <c r="K241" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="242" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A242">
+        <v>8</v>
+      </c>
+      <c r="B242">
         <v>253</v>
       </c>
-      <c r="C167" t="s">
+      <c r="C242" t="s">
         <v>239</v>
       </c>
-      <c r="D167" t="s">
+      <c r="D242" t="s">
         <v>94</v>
       </c>
-      <c r="E167" t="s">
-        <v>147</v>
-      </c>
-      <c r="F167" t="s">
+      <c r="E242" t="s">
+        <v>147</v>
+      </c>
+      <c r="F242" t="s">
         <v>232</v>
       </c>
-      <c r="G167">
+      <c r="G242">
         <v>1770</v>
       </c>
-      <c r="H167" t="s">
+      <c r="H242" t="s">
         <v>232</v>
       </c>
-      <c r="J167" t="s">
-        <v>147</v>
-      </c>
-      <c r="K167" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="168" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B168">
+      <c r="J242" t="s">
+        <v>147</v>
+      </c>
+      <c r="K242" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="243" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A243">
+        <v>8</v>
+      </c>
+      <c r="B243">
         <v>254</v>
       </c>
-      <c r="C168" t="s">
+      <c r="C243" t="s">
         <v>231</v>
       </c>
-      <c r="D168" t="s">
+      <c r="D243" t="s">
         <v>165</v>
       </c>
-      <c r="E168">
+      <c r="E243">
         <v>1739</v>
       </c>
-      <c r="F168" t="s">
+      <c r="F243" t="s">
         <v>227</v>
       </c>
-      <c r="G168">
+      <c r="G243">
         <v>1772</v>
       </c>
-      <c r="H168" t="s">
+      <c r="H243" t="s">
         <v>227</v>
       </c>
-      <c r="J168">
+      <c r="J243">
         <v>1810</v>
       </c>
-      <c r="K168" t="s">
+      <c r="K243" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="169" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B169">
+    <row r="244" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A244">
+        <v>8</v>
+      </c>
+      <c r="B244">
         <v>255</v>
       </c>
-      <c r="C169" t="s">
+      <c r="C244" t="s">
         <v>241</v>
       </c>
-      <c r="D169" t="s">
+      <c r="D244" t="s">
         <v>99</v>
       </c>
-      <c r="E169">
+      <c r="E244">
         <v>1754</v>
       </c>
-      <c r="F169" t="s">
+      <c r="F244" t="s">
         <v>227</v>
       </c>
-      <c r="G169">
+      <c r="G244">
         <v>1772</v>
       </c>
-      <c r="H169" t="s">
+      <c r="H244" t="s">
         <v>227</v>
       </c>
-      <c r="J169">
+      <c r="J244">
         <v>1817</v>
       </c>
-      <c r="K169" t="s">
+      <c r="K244" t="s">
         <v>227</v>
       </c>
     </row>
